--- a/import_template_product_variant/tests/sample_only_required_columns.xlsx
+++ b/import_template_product_variant/tests/sample_only_required_columns.xlsx
@@ -61,10 +61,10 @@
     <t xml:space="preserve">*TMPL*invoice_policy</t>
   </si>
   <si>
-    <t xml:space="preserve">*TMPL*image</t>
-  </si>
-  <si>
-    <t xml:space="preserve">image_variant</t>
+    <t xml:space="preserve">*TMPL*image_1920</t>
+  </si>
+  <si>
+    <t xml:space="preserve">image_variant_1920</t>
   </si>
   <si>
     <t xml:space="preserve">*TMPL*description_sale</t>
@@ -103,7 +103,7 @@
     <t xml:space="preserve">service</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit(s)</t>
+    <t xml:space="preserve">Units</t>
   </si>
   <si>
     <t xml:space="preserve">PROD1_WM</t>
@@ -136,7 +136,7 @@
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot; €&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -159,6 +159,12 @@
       <name val="Arial"/>
       <family val="0"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -202,7 +208,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -216,6 +222,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -225,23 +235,23 @@
     </xf>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="false"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3" customBuiltin="false"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6" customBuiltin="false"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4" customBuiltin="false"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7" customBuiltin="false"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:V1048576"/>
-  <sheetFormatPr defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18.89"/>
@@ -249,13 +259,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="18.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15.28"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="17.4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14.35"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="13.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="14" style="0" width="23.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1023" min="18" style="0" width="8.91"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="1024" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1024" style="0" width="11.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -298,7 +307,7 @@
       <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="0" t="s">
@@ -339,15 +348,15 @@
       <c r="F2" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>25</v>
       </c>
       <c r="H2" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="4"/>
+      <c r="I2" s="5"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="4"/>
+      <c r="M2" s="5"/>
       <c r="R2" s="0" t="s">
         <v>27</v>
       </c>
@@ -376,15 +385,15 @@
       <c r="F3" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>25</v>
       </c>
       <c r="H3" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="4"/>
+      <c r="I3" s="5"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="4"/>
+      <c r="M3" s="5"/>
       <c r="R3" s="0" t="s">
         <v>27</v>
       </c>
@@ -413,15 +422,15 @@
       <c r="F4" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>25</v>
       </c>
       <c r="H4" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="4"/>
+      <c r="I4" s="5"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="4"/>
+      <c r="M4" s="5"/>
       <c r="R4" s="0" t="s">
         <v>27</v>
       </c>
@@ -444,15 +453,15 @@
       <c r="F5" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>25</v>
       </c>
       <c r="H5" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="4"/>
+      <c r="I5" s="5"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="4"/>
+      <c r="M5" s="5"/>
       <c r="R5" s="0" t="s">
         <v>27</v>
       </c>
